--- a/data/export/2026-10-21-浦东35路.xlsx
+++ b/data/export/2026-10-21-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC9"/>
+  <dimension ref="A1:AC21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -715,7 +715,7 @@
       <c r="AB2" s="2" t="inlineStr"/>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -826,7 +826,7 @@
       <c r="AB3" s="2" t="inlineStr"/>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -887,7 +887,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -937,7 +937,7 @@
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1270,7 +1270,7 @@
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1381,7 +1381,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -1389,22 +1389,22 @@
       <c r="A9" s="2" t="inlineStr"/>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>沪A90275D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1437,12 +1437,12 @@
       <c r="M9" s="2" t="inlineStr"/>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1492,7 +1492,1339 @@
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr"/>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr"/>
+      <c r="R10" s="2" t="inlineStr"/>
+      <c r="S10" s="2" t="inlineStr"/>
+      <c r="T10" s="2" t="inlineStr"/>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y10" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>沪A52272D</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr"/>
+      <c r="S11" s="2" t="inlineStr"/>
+      <c r="T11" s="2" t="inlineStr"/>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr"/>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr"/>
+      <c r="S12" s="2" t="inlineStr"/>
+      <c r="T12" s="2" t="inlineStr"/>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="R13" s="2" t="inlineStr"/>
+      <c r="S13" s="2" t="inlineStr"/>
+      <c r="T13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr"/>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr"/>
+      <c r="S14" s="2" t="inlineStr"/>
+      <c r="T14" s="2" t="inlineStr"/>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr"/>
+      <c r="R15" s="2" t="inlineStr"/>
+      <c r="S15" s="2" t="inlineStr"/>
+      <c r="T15" s="2" t="inlineStr"/>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr"/>
+      <c r="R16" s="2" t="inlineStr"/>
+      <c r="S16" s="2" t="inlineStr"/>
+      <c r="T16" s="2" t="inlineStr"/>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr"/>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr"/>
+      <c r="R17" s="2" t="inlineStr"/>
+      <c r="S17" s="2" t="inlineStr"/>
+      <c r="T17" s="2" t="inlineStr"/>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr"/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr"/>
+      <c r="S18" s="2" t="inlineStr"/>
+      <c r="T18" s="2" t="inlineStr"/>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr"/>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr"/>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr"/>
+      <c r="R19" s="2" t="inlineStr"/>
+      <c r="S19" s="2" t="inlineStr"/>
+      <c r="T19" s="2" t="inlineStr"/>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr"/>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr"/>
+      <c r="R20" s="2" t="inlineStr"/>
+      <c r="S20" s="2" t="inlineStr"/>
+      <c r="T20" s="2" t="inlineStr"/>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AC20" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr"/>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr"/>
+      <c r="R21" s="2" t="inlineStr"/>
+      <c r="S21" s="2" t="inlineStr"/>
+      <c r="T21" s="2" t="inlineStr"/>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr"/>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-21-浦东35路.xlsx
+++ b/data/export/2026-10-21-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC21"/>
+  <dimension ref="A1:AC32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -436,20 +436,20 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
-    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
     <col width="16" customWidth="1" min="18" max="18"/>
     <col width="20" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="36" customWidth="1" min="20" max="20"/>
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
@@ -632,32 +632,36 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>152分钟</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -665,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -689,33 +693,37 @@
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" s="2" t="inlineStr"/>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>152.0</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -743,32 +751,36 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:36</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -776,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -800,33 +812,37 @@
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" s="2" t="inlineStr"/>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
+      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -854,32 +870,36 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>153分钟</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -887,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -911,17 +931,17 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
@@ -931,13 +951,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>153.0</t>
+        </is>
+      </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -998,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1037,7 +1061,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1048,7 +1072,7 @@
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1100,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程40%处后消失；随后反向物理轨迹由seq28推进至seq33，推进5站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1109,7 +1133,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1117,10 +1141,22 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q6" s="2" t="inlineStr"/>
-      <c r="R6" s="2" t="inlineStr"/>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>物理seq26（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>07:49</t>
+        </is>
+      </c>
       <c r="S6" s="2" t="inlineStr"/>
-      <c r="T6" s="2" t="inlineStr"/>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq26映射；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
           <t>06:36</t>
@@ -1159,7 +1195,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1270,7 +1306,7 @@
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1367,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1381,7 +1417,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1478,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1492,7 +1528,7 @@
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1553,7 +1589,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1603,7 +1639,7 @@
       <c r="AB10" s="2" t="inlineStr"/>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1664,7 +1700,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1714,7 +1750,7 @@
       <c r="AB11" s="2" t="inlineStr"/>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1775,7 +1811,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1825,7 +1861,7 @@
       <c r="AB12" s="2" t="inlineStr"/>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1886,7 +1922,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1936,7 +1972,7 @@
       <c r="AB13" s="2" t="inlineStr"/>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1997,7 +2033,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2047,7 +2083,7 @@
       <c r="AB14" s="2" t="inlineStr"/>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2108,7 +2144,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2158,7 +2194,7 @@
       <c r="AB15" s="2" t="inlineStr"/>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2219,7 +2255,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2269,7 +2305,7 @@
       <c r="AB16" s="2" t="inlineStr"/>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2330,7 +2366,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2380,7 +2416,7 @@
       <c r="AB17" s="2" t="inlineStr"/>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2441,7 +2477,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2491,7 +2527,7 @@
       <c r="AB18" s="2" t="inlineStr"/>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2552,7 +2588,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2602,7 +2638,7 @@
       <c r="AB19" s="2" t="inlineStr"/>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2663,7 +2699,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2713,7 +2749,7 @@
       <c r="AB20" s="2" t="inlineStr"/>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2774,7 +2810,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2824,7 +2860,1236 @@
       <c r="AB21" s="2" t="inlineStr"/>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr"/>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr"/>
+      <c r="R22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr"/>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr"/>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr"/>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr"/>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr"/>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr"/>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr"/>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr"/>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr"/>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr"/>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr"/>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>沪A36993D</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr"/>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr"/>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr"/>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr"/>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr"/>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr"/>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr"/>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr"/>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr"/>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr"/>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr"/>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr"/>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>08:55</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>08:55</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>152.0</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>2/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr"/>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>沪A68895D</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr"/>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>1/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr"/>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr"/>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr"/>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-21-浦东35路.xlsx
+++ b/data/export/2026-10-21-浦东35路.xlsx
@@ -642,24 +642,24 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>152分钟</t>
+          <t>154分钟</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,12 +718,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>152.0</t>
+          <t>154.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -751,36 +751,32 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>08:36</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>146分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr"/>
       <c r="N3" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -788,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -812,17 +808,17 @@
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
@@ -832,17 +828,13 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB3" s="2" t="inlineStr">
-        <is>
-          <t>146.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB3" s="2" t="inlineStr"/>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -880,24 +872,24 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>153分钟</t>
+          <t>154分钟</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -907,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -956,12 +948,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>154.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1014,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1105,7 +1097,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程40%处后消失；随后反向物理轨迹由seq28推进至seq33，推进5站，达到≥2站确认条件</t>
+          <t>原方向在全程40%处后消失；随后反向物理轨迹由seq28推进至seq39，推进11站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1133,7 +1125,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1256,7 +1248,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1367,7 +1359,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1700,7 +1692,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1811,7 +1803,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1922,7 +1914,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2033,7 +2025,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2144,7 +2136,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2366,7 +2358,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2588,7 +2580,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2699,7 +2691,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2810,7 +2802,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2921,7 +2913,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3032,7 +3024,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3143,7 +3135,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3254,7 +3246,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3365,7 +3357,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3476,7 +3468,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3544,7 +3536,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -3587,7 +3579,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3601,7 +3593,7 @@
       <c r="T28" s="2" t="inlineStr"/>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
@@ -3698,7 +3690,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3766,7 +3758,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -3809,7 +3801,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3823,7 +3815,7 @@
       <c r="T30" s="2" t="inlineStr"/>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
@@ -3858,12 +3850,12 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>152.0</t>
+          <t>154.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -3924,7 +3916,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -3968,17 +3960,13 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB31" s="2" t="inlineStr">
-        <is>
-          <t>146.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr"/>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -4039,7 +4027,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">

--- a/data/export/2026-10-21-浦东35路.xlsx
+++ b/data/export/2026-10-21-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC32"/>
+  <dimension ref="A1:AC38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -642,19 +642,19 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>154分钟</t>
+          <t>164分钟</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,12 +718,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>164.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -751,32 +751,36 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>153分钟</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -784,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -808,17 +812,17 @@
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
@@ -828,13 +832,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>153.0</t>
+        </is>
+      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -862,36 +870,32 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>154分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr"/>
       <c r="N4" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -899,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -923,37 +927,33 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB4" s="2" t="inlineStr">
-        <is>
-          <t>154.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -981,32 +981,36 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>158分钟</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1014,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1038,17 +1042,17 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
@@ -1058,13 +1062,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>158.0</t>
+        </is>
+      </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -1097,7 +1105,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程40%处后消失；随后反向物理轨迹由seq28推进至seq39，推进11站，达到≥2站确认条件</t>
+          <t>原方向在全程40%处后消失；随后反向物理轨迹由seq28推进至seq63，推进35站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1125,7 +1133,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1176,7 +1184,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1215,32 +1223,36 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>158分钟</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -1248,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1272,33 +1284,37 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>158.0</t>
+        </is>
+      </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -1326,32 +1342,36 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>160分钟</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1359,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1383,33 +1403,37 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>160.0</t>
+        </is>
+      </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1509,7 +1533,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1581,7 +1605,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1692,7 +1716,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1770,32 +1794,36 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>155分钟</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -1803,7 +1831,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1827,33 +1855,37 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>155.0</t>
+        </is>
+      </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -1881,12 +1913,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程38%处后消失；随后反向物理轨迹由seq37推进至seq44，推进7站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1914,7 +1946,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1922,10 +1954,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q13" s="2" t="inlineStr"/>
-      <c r="R13" s="2" t="inlineStr"/>
-      <c r="S13" s="2" t="inlineStr"/>
-      <c r="T13" s="2" t="inlineStr"/>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>沪南路高科西路</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>08:51</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>08:56</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq25映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±5分钟；反向位置浦建路锦绣路 ETA 10分钟参与校验</t>
+        </is>
+      </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
           <t>07:12</t>
@@ -2025,7 +2073,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2136,7 +2184,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2247,7 +2295,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2358,7 +2406,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2469,7 +2517,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2580,7 +2628,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2691,7 +2739,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2802,7 +2850,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2913,7 +2961,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3024,7 +3072,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3135,7 +3183,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3246,7 +3294,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3357,7 +3405,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3468,7 +3516,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3579,7 +3627,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3690,7 +3738,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3748,22 +3796,22 @@
       <c r="A30" s="2" t="inlineStr"/>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A68895D</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -3801,7 +3849,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3850,7 +3898,7 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>153.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -3863,22 +3911,22 @@
       <c r="A31" s="2" t="inlineStr"/>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>沪A68895D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>09:05</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -3916,7 +3964,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -3930,7 +3978,7 @@
       <c r="T31" s="2" t="inlineStr"/>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
@@ -3960,13 +4008,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB31" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>164.0</t>
+        </is>
+      </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -3974,22 +4026,22 @@
       <c r="A32" s="2" t="inlineStr"/>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>09:15</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -4027,7 +4079,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4081,6 +4133,688 @@
         </is>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr"/>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>沪A72305D</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr"/>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr"/>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr"/>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr"/>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr"/>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>158.0</t>
+        </is>
+      </c>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>3/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr"/>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr"/>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>158.0</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>3/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr"/>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr"/>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr"/>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr"/>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>160.0</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>5/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr"/>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr"/>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>155.0</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>2/28</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-21-浦东35路.xlsx
+++ b/data/export/2026-10-21-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC38"/>
+  <dimension ref="A1:AC47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -1133,7 +1133,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1605,7 +1605,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1644,7 +1644,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1683,32 +1683,36 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>176分钟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -1716,7 +1720,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1740,33 +1744,37 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
+          <t>176.0</t>
+        </is>
+      </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1839,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1885,7 +1893,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -1918,7 +1926,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程38%处后消失；随后反向物理轨迹由seq37推进至seq44，推进7站，达到≥2站确认条件</t>
+          <t>原方向在全程38%处后消失；随后反向物理轨迹由seq37推进至seq61，推进24站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1946,7 +1954,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2040,32 +2048,36 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>167分钟</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -2073,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2097,33 +2109,37 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
+          <t>167.0</t>
+        </is>
+      </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -2184,7 +2200,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2223,7 +2239,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2262,12 +2278,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程30%处后消失；随后反向物理轨迹由seq39推进至seq56，推进17站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2295,7 +2311,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2303,10 +2319,22 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q16" s="2" t="inlineStr"/>
-      <c r="R16" s="2" t="inlineStr"/>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>物理seq20（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>08:44</t>
+        </is>
+      </c>
       <c r="S16" s="2" t="inlineStr"/>
-      <c r="T16" s="2" t="inlineStr"/>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq20映射；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
           <t>07:24</t>
@@ -2373,32 +2401,36 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>163分钟</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -2406,7 +2438,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2430,33 +2462,37 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
+          <t>163.0</t>
+        </is>
+      </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -2517,7 +2553,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2556,7 +2592,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2595,32 +2631,36 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>151分钟</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -2628,7 +2668,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2652,33 +2692,37 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB19" s="2" t="inlineStr"/>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
+          <t>151.0</t>
+        </is>
+      </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -2706,32 +2750,36 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>174分钟</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -2739,7 +2787,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2763,33 +2811,37 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
+          <t>174.0</t>
+        </is>
+      </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -2850,7 +2902,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2889,7 +2941,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -2961,7 +3013,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3039,32 +3091,36 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>140分钟</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -3072,7 +3128,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3096,17 +3152,17 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
@@ -3116,13 +3172,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB23" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>140.0</t>
+        </is>
+      </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -3183,7 +3243,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3294,7 +3354,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3405,7 +3465,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3516,7 +3576,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3627,7 +3687,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3738,7 +3798,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3849,7 +3909,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3903,7 +3963,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -3964,7 +4024,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4018,7 +4078,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -4079,7 +4139,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4190,7 +4250,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4301,7 +4361,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4355,7 +4415,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -4416,7 +4476,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4470,7 +4530,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -4531,7 +4591,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4589,7 +4649,7 @@
       <c r="A37" s="2" t="inlineStr"/>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -4637,12 +4697,12 @@
       <c r="M37" s="2" t="inlineStr"/>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4686,17 +4746,13 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB37" s="2" t="inlineStr">
-        <is>
-          <t>160.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr"/>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -4704,22 +4760,22 @@
       <c r="A38" s="2" t="inlineStr"/>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>沪A67672D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -4752,12 +4808,12 @@
       <c r="M38" s="2" t="inlineStr"/>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4806,12 +4862,1035 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
+          <t>160.0</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>7/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr"/>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr"/>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr"/>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
           <t>155.0</t>
         </is>
       </c>
-      <c r="AC38" s="2" t="inlineStr">
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>4/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr"/>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr"/>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr"/>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>167.0</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>10/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr"/>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>沪A52272D</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr"/>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr"/>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>176.0</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>12/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr"/>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr"/>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr"/>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr"/>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr"/>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr"/>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>163.0</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr">
+        <is>
+          <t>8/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr"/>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr"/>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr"/>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr"/>
+      <c r="AC44" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr"/>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr"/>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr"/>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>151.0</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr">
         <is>
           <t>2/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr"/>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr"/>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr"/>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr"/>
+      <c r="AC46" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr"/>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr"/>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr"/>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>174.0</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr">
+        <is>
+          <t>11/28</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-21-浦东35路.xlsx
+++ b/data/export/2026-10-21-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC47"/>
+  <dimension ref="A1:AC54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,17 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>164.0</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -942,18 +942,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>137.0</t>
+        </is>
+      </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1057,17 +1061,17 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>158.0</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1133,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1260,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1314,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1433,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1605,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1644,7 +1648,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1720,7 +1724,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1774,7 +1778,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -1839,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1893,7 +1897,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2089,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2139,7 +2143,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -2200,7 +2204,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2438,7 +2442,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2492,7 +2496,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2668,7 +2672,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2722,7 +2726,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -2760,24 +2764,24 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>174分钟</t>
+          <t>170分钟</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2787,7 +2791,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2836,12 +2840,12 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>174.0</t>
+          <t>170.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -2902,7 +2906,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2980,32 +2984,36 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>177分钟</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -3013,7 +3021,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3037,33 +3045,37 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB22" s="2" t="inlineStr"/>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>177.0</t>
+        </is>
+      </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -3128,7 +3140,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3167,14 +3179,14 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
           <t>140.0</t>
@@ -3182,7 +3194,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3255,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3321,32 +3333,36 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>154分钟</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -3354,7 +3370,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3378,33 +3394,37 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB25" s="2" t="inlineStr"/>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>154.0</t>
+        </is>
+      </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -3432,32 +3452,36 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>143分钟</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3465,7 +3489,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3489,17 +3513,17 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
@@ -3509,13 +3533,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB26" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>143.0</t>
+        </is>
+      </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -3576,7 +3604,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3654,32 +3682,36 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>143分钟</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3687,7 +3719,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3711,33 +3743,37 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB28" s="2" t="inlineStr"/>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>143.0</t>
+        </is>
+      </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -3798,7 +3834,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3909,7 +3945,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3963,7 +3999,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -3991,32 +4027,36 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4024,7 +4064,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4048,17 +4088,17 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
@@ -4068,17 +4108,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>164.0</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -4106,32 +4146,36 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4139,7 +4183,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4163,33 +4207,37 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB32" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>137.0</t>
+        </is>
+      </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -4217,12 +4265,12 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程46%处后消失；随后反向物理轨迹由seq28推进至seq49，推进21站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -4250,7 +4298,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4258,10 +4306,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q33" s="2" t="inlineStr"/>
-      <c r="R33" s="2" t="inlineStr"/>
-      <c r="S33" s="2" t="inlineStr"/>
-      <c r="T33" s="2" t="inlineStr"/>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t>物理seq30（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr">
+        <is>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="S33" s="2" t="inlineStr">
+        <is>
+          <t>10:33</t>
+        </is>
+      </c>
+      <c r="T33" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq30映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±7分钟；反向位置物理seq28（站名待映射） ETA 2分钟参与校验</t>
+        </is>
+      </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
           <t>09:24</t>
@@ -4328,32 +4392,36 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4361,7 +4429,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4385,32 +4453,32 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA34" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>158.0</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
@@ -4476,7 +4544,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4530,7 +4598,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -4591,7 +4659,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4702,7 +4770,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4741,7 +4809,7 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
@@ -4813,7 +4881,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4867,7 +4935,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -4928,7 +4996,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -4982,7 +5050,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -5043,7 +5111,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5097,7 +5165,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -5158,7 +5226,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5212,7 +5280,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -5273,7 +5341,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5384,7 +5452,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5438,7 +5506,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -5499,7 +5567,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5610,7 +5678,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5664,7 +5732,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -5725,7 +5793,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5836,7 +5904,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5885,12 +5953,813 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>174.0</t>
+          <t>170.0</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>15/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr"/>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr"/>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr"/>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>140.0</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr">
+        <is>
+          <t>2/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr"/>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr"/>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr"/>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>177.0</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr">
+        <is>
+          <t>17/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr"/>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr"/>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr"/>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>143.0</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr">
+        <is>
+          <t>3/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr"/>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr"/>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr"/>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>154.0</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr">
+        <is>
+          <t>9/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr"/>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr"/>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr"/>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>144.0</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
+          <t>5/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr"/>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr"/>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr"/>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>137.0</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>1/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr"/>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr"/>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr"/>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr"/>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-21-浦东35路.xlsx
+++ b/data/export/2026-10-21-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC54"/>
+  <dimension ref="A1:AC60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -957,7 +957,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1071,12 +1071,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1199,7 +1199,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1308,17 +1308,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>158.0</t>
+          <t>147.5</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1427,17 +1427,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>160.0</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1537,7 +1537,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1659,7 +1659,7 @@
       <c r="AB10" s="2" t="inlineStr"/>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>176.0</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1897,7 +1897,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -1958,7 +1958,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2024,7 +2024,7 @@
       <c r="AB13" s="2" t="inlineStr"/>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -2089,7 +2089,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2128,22 +2128,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>167.0</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2254,7 +2254,7 @@
       <c r="AB15" s="2" t="inlineStr"/>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2315,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2366,7 +2366,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       <c r="AB16" s="2" t="inlineStr"/>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2486,17 +2486,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>163.0</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2607,7 +2607,7 @@
       <c r="AB18" s="2" t="inlineStr"/>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2711,7 +2711,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2845,7 +2845,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2956,7 +2956,7 @@
       <c r="AB21" s="2" t="inlineStr"/>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -3021,7 +3021,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -3140,7 +3140,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3194,7 +3194,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -3305,7 +3305,7 @@
       <c r="AB24" s="2" t="inlineStr"/>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -3370,7 +3370,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -3543,7 +3543,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -3654,7 +3654,7 @@
       <c r="AB27" s="2" t="inlineStr"/>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -3719,7 +3719,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3773,7 +3773,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -3884,7 +3884,7 @@
       <c r="AB29" s="2" t="inlineStr"/>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -3999,7 +3999,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -4183,7 +4183,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4237,7 +4237,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -4270,7 +4270,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程46%处后消失；随后反向物理轨迹由seq28推进至seq49，推进21站，达到≥2站确认条件</t>
+          <t>原方向在全程46%处后消失；随后反向物理轨迹由seq28推进至seq62，推进34站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -4298,7 +4298,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4364,7 +4364,7 @@
       <c r="AB33" s="2" t="inlineStr"/>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -4402,24 +4402,24 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>130分钟</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4429,7 +4429,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4478,12 +4478,12 @@
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -4511,32 +4511,36 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -4544,7 +4548,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4568,17 +4572,17 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
@@ -4588,17 +4592,17 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>158.0</t>
+          <t>147.5</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -4659,7 +4663,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4698,7 +4702,7 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
@@ -4709,7 +4713,7 @@
       <c r="AB36" s="2" t="inlineStr"/>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -4770,7 +4774,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4820,7 +4824,7 @@
       <c r="AB37" s="2" t="inlineStr"/>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -4848,32 +4852,36 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4881,7 +4889,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4905,17 +4913,17 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
@@ -4925,17 +4933,17 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>160.0</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -4996,7 +5004,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5050,7 +5058,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -5078,32 +5086,36 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -5111,7 +5123,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5135,37 +5147,37 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA40" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>167.0</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -5193,32 +5205,36 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>122分钟</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -5226,7 +5242,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5250,17 +5266,17 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
@@ -5270,17 +5286,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>176.0</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -5341,7 +5357,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5391,7 +5407,7 @@
       <c r="AB42" s="2" t="inlineStr"/>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -5419,32 +5435,36 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -5452,7 +5472,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5476,17 +5496,17 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
@@ -5496,17 +5516,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>163.0</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -5567,7 +5587,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5617,7 +5637,7 @@
       <c r="AB44" s="2" t="inlineStr"/>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -5678,7 +5698,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5717,7 +5737,7 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
@@ -5732,7 +5752,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -5793,7 +5813,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5843,7 +5863,7 @@
       <c r="AB46" s="2" t="inlineStr"/>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -5904,7 +5924,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5958,7 +5978,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -6019,7 +6039,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6073,7 +6093,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -6134,7 +6154,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6188,7 +6208,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -6249,7 +6269,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6303,7 +6323,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -6364,7 +6384,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6418,7 +6438,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -6479,7 +6499,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6528,12 +6548,12 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -6594,7 +6614,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6648,7 +6668,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -6709,7 +6729,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6759,7 +6779,681 @@
       <c r="AB54" s="2" t="inlineStr"/>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr"/>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr"/>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr"/>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr"/>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr"/>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>沪A79307D</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr"/>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>09:54</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr"/>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr"/>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr"/>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr"/>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr"/>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr"/>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr"/>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr"/>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr"/>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>147.0</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>7/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr"/>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr"/>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr"/>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr"/>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr"/>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr"/>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr"/>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>151.0</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>12/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-21-浦东35路.xlsx
+++ b/data/export/2026-10-21-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC60"/>
+  <dimension ref="A1:AC66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -957,7 +957,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -1897,7 +1897,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -1958,7 +1958,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2143,7 +2143,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2315,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2442,7 +2442,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2496,7 +2496,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2596,18 +2596,22 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB18" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -2672,7 +2676,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2716,17 +2720,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>151.0</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -2791,7 +2795,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2845,7 +2849,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -2906,7 +2910,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2950,13 +2954,17 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB21" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -3021,7 +3029,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3060,17 +3068,17 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>177.0</t>
+          <t>153.5</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
@@ -3140,7 +3148,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3179,17 +3187,17 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>131.5</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
@@ -3370,7 +3378,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3414,17 +3422,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>147.5</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -3489,7 +3497,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3528,14 +3536,14 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
           <t>143.0</t>
@@ -3543,7 +3551,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -3719,7 +3727,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3758,22 +3766,22 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA28" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -3999,7 +4007,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4126,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -4183,7 +4191,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4237,7 +4245,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -4429,7 +4437,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4468,7 +4476,7 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
@@ -4483,7 +4491,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -4602,7 +4610,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -4663,7 +4671,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4774,7 +4782,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4943,7 +4951,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -5058,7 +5066,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -5123,7 +5131,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5177,7 +5185,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -5296,7 +5304,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -5472,7 +5480,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5526,7 +5534,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -5554,32 +5562,36 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -5587,7 +5599,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5611,33 +5623,37 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB44" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -5665,32 +5681,36 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -5698,7 +5718,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5722,17 +5742,17 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
@@ -5742,17 +5762,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>151.0</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -5780,32 +5800,36 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -5813,7 +5837,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5837,17 +5861,17 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr">
@@ -5857,13 +5881,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB46" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -5924,7 +5952,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5978,7 +6006,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -6006,32 +6034,36 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>123分钟</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M48" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -6039,7 +6071,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6063,32 +6095,32 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y48" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA48" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>131.5</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
@@ -6121,32 +6153,36 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -6154,7 +6190,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6178,32 +6214,32 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y49" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA49" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>177.0</t>
+          <t>153.5</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
@@ -6236,32 +6272,36 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6269,7 +6309,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6293,37 +6333,37 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y50" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA50" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -6351,32 +6391,36 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>141分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -6384,7 +6428,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6408,17 +6452,17 @@
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y51" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z51" s="2" t="inlineStr">
@@ -6428,17 +6472,17 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>147.5</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -6499,7 +6543,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6538,7 +6582,7 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
@@ -6553,7 +6597,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -6614,7 +6658,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6668,7 +6712,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -6729,7 +6773,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6840,7 +6884,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6951,7 +6995,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7062,7 +7106,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7173,7 +7217,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7227,7 +7271,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -7288,7 +7332,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7399,7 +7443,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7443,17 +7487,707 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>139.0</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>6/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr"/>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr"/>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr"/>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB60" s="2" t="inlineStr">
-        <is>
-          <t>151.0</t>
-        </is>
-      </c>
-      <c r="AC60" s="2" t="inlineStr">
-        <is>
-          <t>12/29</t>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>3/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr"/>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr"/>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr"/>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>131.5</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>2/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr"/>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr"/>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr"/>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>153.5</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>17/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr"/>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr"/>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr"/>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>136.5</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>4/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr"/>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>沪A36993D</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr"/>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr"/>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>143.0</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>9/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr"/>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr"/>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr"/>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>141.5</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>7/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-21-浦东35路.xlsx
+++ b/data/export/2026-10-21-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC66"/>
+  <dimension ref="A1:AC68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -947,17 +947,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1066,17 +1066,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>138.7</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1648,7 +1648,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2143,7 +2143,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2315,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2496,7 +2496,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2676,7 +2676,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2730,7 +2730,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3148,7 +3148,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3378,7 +3378,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>147.5</t>
+          <t>146.5</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -3497,7 +3497,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3727,7 +3727,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -4072,7 +4072,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4111,7 +4111,7 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4235,17 +4235,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -4437,7 +4437,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>138.7</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -4610,7 +4610,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -4671,7 +4671,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4782,7 +4782,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4821,7 +4821,7 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -5534,7 +5534,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -5599,7 +5599,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5718,7 +5718,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5772,7 +5772,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -6071,7 +6071,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6190,7 +6190,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6309,7 +6309,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6363,7 +6363,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -6401,12 +6401,12 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>141分钟</t>
+          <t>139分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
@@ -6428,7 +6428,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6477,12 +6477,12 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>147.5</t>
+          <t>146.5</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -6510,32 +6510,36 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6543,7 +6547,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6567,17 +6571,17 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y52" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z52" s="2" t="inlineStr">
@@ -6587,17 +6591,17 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>138.7</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -6625,32 +6629,36 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M53" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6658,7 +6666,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6682,17 +6690,17 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y53" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z53" s="2" t="inlineStr">
@@ -6702,17 +6710,17 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -6773,7 +6781,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6812,7 +6820,7 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA54" s="2" t="inlineStr">
@@ -6884,7 +6892,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6962,12 +6970,12 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程38%处后消失；随后反向物理轨迹由seq38推进至seq41，推进3站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -6995,18 +7003,34 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr">
+        <is>
+          <t>沪南路高科西路</t>
+        </is>
+      </c>
+      <c r="R56" s="2" t="inlineStr">
+        <is>
           <t>13:21</t>
         </is>
       </c>
-      <c r="P56" s="2" t="inlineStr">
-        <is>
-          <t>SHMAAS</t>
-        </is>
-      </c>
-      <c r="Q56" s="2" t="inlineStr"/>
-      <c r="R56" s="2" t="inlineStr"/>
-      <c r="S56" s="2" t="inlineStr"/>
-      <c r="T56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="T56" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq25映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±5分钟；反向位置物理seq38（站名待映射） ETA 9分钟参与校验</t>
+        </is>
+      </c>
       <c r="U56" s="2" t="inlineStr">
         <is>
           <t>12:30</t>
@@ -7106,7 +7130,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7217,7 +7241,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7271,7 +7295,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -7332,7 +7356,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7443,7 +7467,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7497,7 +7521,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -7558,7 +7582,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7673,7 +7697,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7788,7 +7812,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7903,7 +7927,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -7957,7 +7981,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -8018,7 +8042,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8133,7 +8157,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8177,17 +8201,243 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>138.7</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>6/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr"/>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr"/>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr"/>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB66" s="2" t="inlineStr">
-        <is>
-          <t>141.5</t>
-        </is>
-      </c>
-      <c r="AC66" s="2" t="inlineStr">
-        <is>
-          <t>7/29</t>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>149.0</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>14/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr"/>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr"/>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr"/>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr"/>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-21-浦东35路.xlsx
+++ b/data/export/2026-10-21-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC68"/>
+  <dimension ref="A1:AC71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -952,12 +952,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>132.5</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1422,14 +1422,14 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
           <t>142.5</t>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1542,13 +1542,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1653,13 +1657,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB10" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -1724,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1763,14 +1771,14 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
           <t>149.0</t>
@@ -1778,7 +1786,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -1897,7 +1905,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -1958,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2013,18 +2021,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB13" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
+          <t>138.0</t>
+        </is>
+      </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -2089,7 +2101,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2143,7 +2155,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2496,7 +2508,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2569,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2611,7 +2623,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2688,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2730,7 +2742,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -2849,7 +2861,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -2964,7 +2976,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -3029,7 +3041,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3083,7 +3095,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -3148,7 +3160,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3202,7 +3214,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3444,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -3497,7 +3509,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3551,7 +3563,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -3727,7 +3739,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3781,7 +3793,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -4007,7 +4019,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -4072,7 +4084,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4126,7 +4138,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -4191,7 +4203,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4240,12 +4252,12 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>132.5</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -4437,7 +4449,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4491,7 +4503,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -4610,7 +4622,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -4671,7 +4683,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4715,13 +4727,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB36" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -4782,7 +4798,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4826,13 +4842,17 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB37" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -4897,7 +4917,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4936,14 +4956,14 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA38" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
           <t>142.5</t>
@@ -4951,7 +4971,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -5066,7 +5086,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -5131,7 +5151,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5185,7 +5205,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -5250,7 +5270,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5289,14 +5309,14 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA41" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
           <t>149.0</t>
@@ -5304,7 +5324,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -5534,7 +5554,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -5599,7 +5619,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5653,7 +5673,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -5718,7 +5738,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5772,7 +5792,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -5891,7 +5911,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6026,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -6071,7 +6091,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6125,7 +6145,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -6190,7 +6210,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6244,7 +6264,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -6309,7 +6329,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6363,7 +6383,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -6482,7 +6502,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -6547,7 +6567,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6601,7 +6621,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -6639,19 +6659,19 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>132分钟</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
@@ -6666,7 +6686,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6715,12 +6735,12 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>132.5</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -6748,32 +6768,36 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M54" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -6781,7 +6805,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6805,17 +6829,17 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y54" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z54" s="2" t="inlineStr">
@@ -6825,13 +6849,17 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB54" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -6859,32 +6887,36 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M55" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -6892,7 +6924,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6916,17 +6948,17 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y55" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z55" s="2" t="inlineStr">
@@ -6936,13 +6968,17 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB55" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -6975,7 +7011,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程38%处后消失；随后反向物理轨迹由seq38推进至seq41，推进3站，达到≥2站确认条件</t>
+          <t>原方向在全程38%处后消失；随后反向物理轨迹由seq38推进至seq52，推进14站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -7003,7 +7039,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7097,32 +7133,36 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>138分钟</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M57" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -7130,7 +7170,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7154,33 +7194,37 @@
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y57" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB57" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>138.0</t>
+        </is>
+      </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -7241,7 +7285,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7295,7 +7339,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -7356,7 +7400,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7467,7 +7511,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7521,7 +7565,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -7582,7 +7626,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7636,7 +7680,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -7697,7 +7741,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7751,7 +7795,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -7812,7 +7856,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7866,7 +7910,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -7927,7 +7971,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -7981,7 +8025,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -8042,7 +8086,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8096,7 +8140,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -8157,7 +8201,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8211,7 +8255,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -8272,7 +8316,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8326,7 +8370,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -8387,7 +8431,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8431,13 +8475,362 @@
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB68" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>2/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr"/>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr"/>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr"/>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>142.5</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>11/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr"/>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr"/>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr"/>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>138.0</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>8/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr"/>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>沪A52272D</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr"/>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr"/>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>149.0</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>17/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-21-浦东35路.xlsx
+++ b/data/export/2026-10-21-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC71"/>
+  <dimension ref="A1:AC75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -957,7 +957,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1199,7 +1199,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1667,7 +1667,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -1905,7 +1905,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2145,17 +2145,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>140.3</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2255,7 +2255,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2266,7 +2266,7 @@
       <c r="AB15" s="2" t="inlineStr"/>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2383,13 +2383,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB16" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2512,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -2569,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2613,17 +2617,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2732,17 +2736,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2865,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -2976,7 +2980,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -3041,7 +3045,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3095,7 +3099,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -3160,7 +3164,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3204,17 +3208,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>131.5</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -3275,7 +3279,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3314,7 +3318,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
@@ -3325,7 +3329,7 @@
       <c r="AB24" s="2" t="inlineStr"/>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -3444,7 +3448,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -3509,7 +3513,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3563,7 +3567,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3678,7 @@
       <c r="AB27" s="2" t="inlineStr"/>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -3739,7 +3743,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3793,7 +3797,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -3904,7 +3908,7 @@
       <c r="AB29" s="2" t="inlineStr"/>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -4019,7 +4023,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -4084,7 +4088,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4138,7 +4142,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -4257,7 +4261,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -4318,7 +4322,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4373,7 +4377,7 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
@@ -4384,7 +4388,7 @@
       <c r="AB33" s="2" t="inlineStr"/>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -4449,7 +4453,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4503,7 +4507,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -4622,7 +4626,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -4683,7 +4687,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4732,12 +4736,12 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -4798,7 +4802,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4852,7 +4856,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -4917,7 +4921,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4971,7 +4975,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -5086,7 +5090,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -5151,7 +5155,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5195,17 +5199,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>140.3</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -5270,7 +5274,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5324,7 +5328,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -5385,7 +5389,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5424,7 +5428,7 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
@@ -5435,7 +5439,7 @@
       <c r="AB42" s="2" t="inlineStr"/>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -5554,7 +5558,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -5619,7 +5623,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5663,17 +5667,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -5738,7 +5742,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5782,17 +5786,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -5911,7 +5915,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -6026,7 +6030,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6095,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6135,17 +6139,17 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>131.5</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -6210,7 +6214,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6264,7 +6268,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -6329,7 +6333,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6383,7 +6387,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -6502,7 +6506,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -6567,7 +6571,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6621,7 +6625,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -6740,7 +6744,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -6805,7 +6809,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6859,7 +6863,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -6897,24 +6901,24 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>126分钟</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6924,7 +6928,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6973,12 +6977,12 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -7011,7 +7015,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程38%处后消失；随后反向物理轨迹由seq38推进至seq52，推进14站，达到≥2站确认条件</t>
+          <t>原方向在全程38%处后消失；随后反向物理轨迹由seq38推进至seq58，推进20站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -7039,7 +7043,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7105,7 +7109,7 @@
       <c r="AB56" s="2" t="inlineStr"/>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -7143,24 +7147,24 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>138分钟</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -7170,7 +7174,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7219,12 +7223,12 @@
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -7252,32 +7256,36 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M58" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -7285,7 +7293,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7309,17 +7317,17 @@
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z58" s="2" t="inlineStr">
@@ -7329,17 +7337,17 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>140.3</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -7367,32 +7375,36 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M59" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -7400,7 +7412,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7424,17 +7436,17 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z59" s="2" t="inlineStr">
@@ -7444,13 +7456,17 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB59" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -7478,32 +7494,36 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M60" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -7511,7 +7531,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7535,17 +7555,17 @@
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y60" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z60" s="2" t="inlineStr">
@@ -7555,17 +7575,17 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -7593,32 +7613,36 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M61" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -7626,7 +7650,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7650,17 +7674,17 @@
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y61" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z61" s="2" t="inlineStr">
@@ -7670,17 +7694,17 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -7708,32 +7732,36 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M62" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -7741,7 +7769,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7765,17 +7793,17 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y62" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z62" s="2" t="inlineStr">
@@ -7785,17 +7813,17 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>131.5</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -7856,7 +7884,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7910,7 +7938,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -7971,7 +7999,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8025,7 +8053,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -8086,7 +8114,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8140,7 +8168,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -8201,7 +8229,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8255,7 +8283,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -8316,7 +8344,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8370,7 +8398,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -8431,7 +8459,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8485,7 +8513,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -8546,7 +8574,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8600,7 +8628,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -8661,7 +8689,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8710,12 +8738,12 @@
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -8776,7 +8804,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8830,7 +8858,451 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr"/>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>沪A72305D</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr"/>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr"/>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr"/>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>—/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr"/>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>沪A15330A</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr"/>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr"/>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr"/>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>—/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr"/>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr"/>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr"/>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr"/>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>—/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr"/>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr"/>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr"/>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr"/>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>—/30</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-21-浦东35路.xlsx
+++ b/data/export/2026-10-21-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC75"/>
+  <dimension ref="A1:AC84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,17 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>144.7</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -942,7 +942,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1066,12 +1066,12 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>138.7</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,14 +1303,14 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
           <t>147.5</t>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1537,7 +1537,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2327,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2378,7 +2378,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2512,7 +2512,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2811,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2850,7 +2850,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -3045,7 +3045,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3089,17 +3089,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>153.5</t>
+          <t>148.3</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -3164,7 +3164,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3279,7 +3279,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3394,7 +3394,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3433,14 +3433,14 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
           <t>146.5</t>
@@ -3448,7 +3448,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -3513,7 +3513,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3557,17 +3557,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3667,7 +3667,7 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3743,7 +3743,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3787,17 +3787,17 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -3969,7 +3969,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4008,7 +4008,7 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
@@ -4023,7 +4023,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -4088,7 +4088,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4132,17 +4132,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>144.7</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -4207,7 +4207,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4246,7 +4246,7 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
@@ -4322,7 +4322,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4497,12 +4497,12 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>138.7</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
@@ -4572,7 +4572,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4611,14 +4611,14 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA35" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
           <t>147.5</t>
@@ -4626,7 +4626,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -4687,7 +4687,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4726,7 +4726,7 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
@@ -4802,7 +4802,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4921,7 +4921,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4975,7 +4975,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -5036,7 +5036,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5075,7 +5075,7 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
@@ -5274,7 +5274,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5328,7 +5328,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -5389,7 +5389,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5558,7 +5558,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -5623,7 +5623,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5677,7 +5677,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -5976,7 +5976,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6015,7 +6015,7 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
@@ -6095,7 +6095,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6214,7 +6214,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6258,17 +6258,17 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>153.5</t>
+          <t>148.3</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -6333,7 +6333,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6377,17 +6377,17 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -6452,7 +6452,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6491,14 +6491,14 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA51" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
           <t>146.5</t>
@@ -6506,7 +6506,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -6571,7 +6571,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6615,12 +6615,12 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>138.7</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
@@ -6690,7 +6690,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6729,7 +6729,7 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA53" s="2" t="inlineStr">
@@ -6809,7 +6809,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6928,7 +6928,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6967,7 +6967,7 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
@@ -7174,7 +7174,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7228,7 +7228,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
@@ -7650,7 +7650,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7704,7 +7704,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -7754,12 +7754,12 @@
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -7769,7 +7769,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7851,32 +7851,36 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>138分钟</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M63" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -7884,7 +7888,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7908,17 +7912,17 @@
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y63" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z63" s="2" t="inlineStr">
@@ -7928,17 +7932,17 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>153.5</t>
+          <t>148.3</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -7966,32 +7970,36 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M64" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -7999,7 +8007,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8023,17 +8031,17 @@
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y64" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z64" s="2" t="inlineStr">
@@ -8043,17 +8051,17 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -8081,32 +8089,36 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>140分钟</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M65" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8114,7 +8126,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8138,17 +8150,17 @@
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y65" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z65" s="2" t="inlineStr">
@@ -8158,17 +8170,17 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -8196,32 +8208,36 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M66" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8229,7 +8245,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8253,17 +8269,17 @@
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y66" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z66" s="2" t="inlineStr">
@@ -8273,12 +8289,12 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>138.7</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
@@ -8311,32 +8327,36 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M67" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8344,7 +8364,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8368,17 +8388,17 @@
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y67" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z67" s="2" t="inlineStr">
@@ -8388,17 +8408,17 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>144.7</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -8459,7 +8479,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8574,7 +8594,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8628,7 +8648,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -8689,7 +8709,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8743,7 +8763,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -8804,7 +8824,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8858,7 +8878,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -8919,7 +8939,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9030,7 +9050,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9141,7 +9161,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9199,22 +9219,22 @@
       <c r="A75" s="2" t="inlineStr"/>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
-        <is>
-          <t>16:01</t>
-        </is>
-      </c>
-      <c r="E75" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -9247,12 +9267,12 @@
       <c r="M75" s="2" t="inlineStr"/>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9291,7 +9311,7 @@
       </c>
       <c r="Z75" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA75" s="2" t="inlineStr">
@@ -9303,6 +9323,1037 @@
       <c r="AC75" s="2" t="inlineStr">
         <is>
           <t>—/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr"/>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr"/>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr"/>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr"/>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>—/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr"/>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr"/>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr"/>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>2/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr"/>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr"/>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr"/>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>170.0</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>23/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr"/>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr"/>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr"/>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>146.5</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>16/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr"/>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>沪A68895D</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr"/>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr"/>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>153.0</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>21/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr"/>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr"/>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr"/>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>132.5</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr">
+        <is>
+          <t>6/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr"/>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr"/>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr"/>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>147.5</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>18/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr"/>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr"/>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr"/>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr">
+        <is>
+          <t>1/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr"/>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr"/>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr"/>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>155.0</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr">
+        <is>
+          <t>22/30</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-21-浦东35路.xlsx
+++ b/data/export/2026-10-21-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC84"/>
+  <dimension ref="A1:AC91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,17 +708,17 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>144.7</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1071,12 +1071,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1422,22 +1422,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>139.7</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1657,17 +1657,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>131.5</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2026,17 +2026,17 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2140,14 +2140,14 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
           <t>140.3</t>
@@ -2155,7 +2155,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2327,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2458,7 +2458,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2497,7 +2497,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2692,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2731,7 +2731,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2865,7 +2865,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -2980,7 +2980,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -3164,7 +3164,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3203,14 +3203,14 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
           <t>129.0</t>
@@ -3218,7 +3218,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3323,13 +3323,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB24" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>160.0</t>
+        </is>
+      </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3398,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3513,7 +3517,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3552,14 +3556,14 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
           <t>141.5</t>
@@ -3567,7 +3571,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3632,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3969,7 +3973,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4088,7 +4092,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4127,17 +4131,17 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>144.7</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4207,7 +4211,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4322,7 +4326,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4453,7 +4457,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4502,12 +4506,12 @@
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -4572,7 +4576,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4687,7 +4691,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4802,7 +4806,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4846,17 +4850,17 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>131.5</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -4921,7 +4925,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4960,22 +4964,22 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA38" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>139.7</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -5036,7 +5040,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5155,7 +5159,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5194,14 +5198,14 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA40" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
           <t>140.3</t>
@@ -5209,7 +5213,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -5274,7 +5278,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5389,7 +5393,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5504,7 +5508,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5543,7 +5547,7 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
@@ -5742,7 +5746,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5781,7 +5785,7 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
@@ -5915,7 +5919,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -5976,7 +5980,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6030,7 +6034,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -6095,7 +6099,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6134,14 +6138,14 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA48" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
           <t>129.0</t>
@@ -6149,7 +6153,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -6452,7 +6456,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6571,7 +6575,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6620,12 +6624,12 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -6690,7 +6694,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6809,7 +6813,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6853,17 +6857,17 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>131.5</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -6928,7 +6932,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7174,7 +7178,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7218,17 +7222,17 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -7293,7 +7297,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7332,14 +7336,14 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA58" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
           <t>140.3</t>
@@ -7347,7 +7351,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7416,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7531,7 +7535,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7570,7 +7574,7 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
@@ -7769,7 +7773,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7808,14 +7812,14 @@
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA62" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
           <t>129.0</t>
@@ -7823,7 +7827,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -8126,7 +8130,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8165,14 +8169,14 @@
       </c>
       <c r="Z65" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA65" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
           <t>141.5</t>
@@ -8180,7 +8184,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -8218,12 +8222,12 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>136分钟</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
@@ -8245,7 +8249,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8294,12 +8298,12 @@
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -8337,24 +8341,24 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>136分钟</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -8364,7 +8368,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8403,17 +8407,17 @@
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA67" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>144.7</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
@@ -8446,32 +8450,36 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M68" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -8479,7 +8487,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8503,17 +8511,17 @@
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y68" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z68" s="2" t="inlineStr">
@@ -8523,17 +8531,17 @@
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>131.5</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -8561,32 +8569,36 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M69" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8594,7 +8606,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8618,37 +8630,37 @@
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y69" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z69" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA69" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>139.7</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -8676,32 +8688,36 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>143分钟</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M70" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -8709,7 +8725,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8733,17 +8749,17 @@
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y70" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z70" s="2" t="inlineStr">
@@ -8753,17 +8769,17 @@
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -8824,7 +8840,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8906,12 +8922,12 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程41%处后消失；随后反向物理轨迹由seq28推进至seq43，推进15站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -8939,7 +8955,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8947,10 +8963,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q72" s="2" t="inlineStr"/>
-      <c r="R72" s="2" t="inlineStr"/>
-      <c r="S72" s="2" t="inlineStr"/>
-      <c r="T72" s="2" t="inlineStr"/>
+      <c r="Q72" s="2" t="inlineStr">
+        <is>
+          <t>物理seq27（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R72" s="2" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="S72" s="2" t="inlineStr">
+        <is>
+          <t>16:32</t>
+        </is>
+      </c>
+      <c r="T72" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq27映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±8分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="U72" s="2" t="inlineStr">
         <is>
           <t>15:35</t>
@@ -9128,32 +9160,36 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>160分钟</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M74" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9161,7 +9197,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9185,17 +9221,17 @@
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y74" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z74" s="2" t="inlineStr">
@@ -9205,13 +9241,17 @@
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB74" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>160.0</t>
+        </is>
+      </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -9272,7 +9312,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9383,7 +9423,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9494,7 +9534,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9609,7 +9649,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9663,7 +9703,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -9724,7 +9764,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9839,7 +9879,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9954,7 +9994,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10069,7 +10109,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10184,7 +10224,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10299,7 +10339,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10357,6 +10397,811 @@
         </is>
       </c>
     </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr"/>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>沪A36993D</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr"/>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr"/>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr"/>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>141.5</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr">
+        <is>
+          <t>14/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr"/>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr"/>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr"/>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr"/>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>140.3</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr">
+        <is>
+          <t>13/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr"/>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr"/>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr"/>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr"/>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>147.0</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr">
+        <is>
+          <t>17/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr"/>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr"/>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr"/>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr"/>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr">
+        <is>
+          <t>7/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr"/>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr"/>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr"/>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr"/>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>145.0</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr">
+        <is>
+          <t>15/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr"/>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr"/>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr"/>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr"/>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="V90" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W90" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y90" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z90" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA90" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB90" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr">
+        <is>
+          <t>3/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr"/>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr"/>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr"/>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr"/>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>139.7</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr">
+        <is>
+          <t>12/30</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-21-浦东35路.xlsx
+++ b/data/export/2026-10-21-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC91"/>
+  <dimension ref="A1:AC98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -957,7 +957,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1667,7 +1667,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1771,22 +1771,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1905,7 +1905,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2021,17 +2021,17 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2101,7 +2101,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2260,13 +2260,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB15" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2331,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2458,7 +2462,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2512,7 +2516,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2577,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2612,7 +2616,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2627,7 +2631,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2696,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2746,7 +2750,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2815,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2855,7 +2859,7 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
@@ -2926,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2965,7 +2969,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -3099,7 +3103,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -3164,7 +3168,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3279,7 +3283,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3318,22 +3322,18 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB24" s="2" t="inlineStr">
-        <is>
-          <t>160.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr"/>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -3398,7 +3398,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3452,7 +3452,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3571,7 +3571,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -3632,7 +3632,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3801,7 +3801,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -3973,7 +3973,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4012,7 +4012,7 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
@@ -4027,7 +4027,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -4092,7 +4092,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -4211,7 +4211,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4265,7 +4265,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -4326,7 +4326,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -4576,7 +4576,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4630,7 +4630,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -4691,7 +4691,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4860,7 +4860,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4925,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4979,7 +4979,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -5040,7 +5040,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5094,7 +5094,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -5159,7 +5159,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5213,7 +5213,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -5278,7 +5278,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5317,22 +5317,22 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA41" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -5393,7 +5393,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5437,13 +5437,17 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB42" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -5508,7 +5512,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5562,7 +5566,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -5627,7 +5631,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5666,7 +5670,7 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
@@ -5681,7 +5685,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -5746,7 +5750,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5800,7 +5804,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -5865,7 +5869,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5904,7 +5908,7 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
@@ -5980,7 +5984,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6024,7 +6028,7 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
@@ -6099,7 +6103,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6272,7 +6276,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -6391,7 +6395,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -6456,7 +6460,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6510,7 +6514,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -6629,7 +6633,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -6694,7 +6698,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6748,7 +6752,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -6867,7 +6871,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -6932,7 +6936,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7178,7 +7182,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7217,17 +7221,17 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
@@ -7297,7 +7301,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7351,7 +7355,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -7416,7 +7420,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7535,7 +7539,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7589,7 +7593,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -7654,7 +7658,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7693,7 +7697,7 @@
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA61" s="2" t="inlineStr">
@@ -7708,7 +7712,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -7773,7 +7777,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7946,7 +7950,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -8065,7 +8069,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -8130,7 +8134,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8184,7 +8188,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -8303,7 +8307,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -8368,7 +8372,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8422,7 +8426,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -8541,7 +8545,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -8606,7 +8610,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8660,7 +8664,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -8688,36 +8692,32 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>143分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
-        </is>
-      </c>
-      <c r="M70" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr"/>
       <c r="N70" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -8725,7 +8725,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8749,32 +8749,32 @@
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y70" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
@@ -8807,32 +8807,36 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M71" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -8840,7 +8844,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8864,37 +8868,37 @@
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y71" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA71" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -8927,7 +8931,7 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程41%处后消失；随后反向物理轨迹由seq28推进至seq43，推进15站，达到≥2站确认条件</t>
+          <t>原方向在全程41%处后消失；随后反向物理轨迹由seq28推进至seq58，推进30站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -8955,7 +8959,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9160,36 +9164,32 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>160分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="M74" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr"/>
       <c r="N74" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9197,7 +9197,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9221,37 +9221,33 @@
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X74" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y74" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z74" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB74" s="2" t="inlineStr">
-        <is>
-          <t>160.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr"/>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -9312,7 +9308,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9351,7 +9347,7 @@
       </c>
       <c r="Z75" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA75" s="2" t="inlineStr">
@@ -9390,32 +9386,36 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M76" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -9423,7 +9423,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9447,17 +9447,17 @@
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y76" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z76" s="2" t="inlineStr">
@@ -9467,13 +9467,17 @@
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB76" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -9534,7 +9538,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9616,32 +9620,36 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>170分钟</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M78" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -9649,7 +9657,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9673,17 +9681,17 @@
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z78" s="2" t="inlineStr">
@@ -9693,7 +9701,7 @@
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
@@ -9764,7 +9772,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9818,7 +9826,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -9879,7 +9887,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9918,7 +9926,7 @@
       </c>
       <c r="Z80" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA80" s="2" t="inlineStr">
@@ -9933,7 +9941,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -9994,7 +10002,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10048,7 +10056,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -10109,7 +10117,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10163,7 +10171,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -10224,7 +10232,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10339,7 +10347,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10393,7 +10401,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -10454,7 +10462,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10508,7 +10516,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -10569,7 +10577,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10623,7 +10631,7 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -10684,7 +10692,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10738,7 +10746,7 @@
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -10799,7 +10807,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10853,7 +10861,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -10914,7 +10922,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -10968,7 +10976,7 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -11029,7 +11037,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11144,7 +11152,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11198,7 +11206,804 @@
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>13/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr"/>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr"/>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr"/>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr"/>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA92" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr">
+        <is>
+          <t>135.0</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr">
+        <is>
+          <t>11/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr"/>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr"/>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr"/>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr"/>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
+          <t>4/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr"/>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr"/>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr"/>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr"/>
+      <c r="R94" s="2" t="inlineStr"/>
+      <c r="S94" s="2" t="inlineStr"/>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr"/>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
+          <t>—/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr"/>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr"/>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr"/>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr"/>
+      <c r="R95" s="2" t="inlineStr"/>
+      <c r="S95" s="2" t="inlineStr"/>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>134.5</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>10/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr"/>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr"/>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr"/>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr"/>
+      <c r="R96" s="2" t="inlineStr"/>
+      <c r="S96" s="2" t="inlineStr"/>
+      <c r="T96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="V96" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W96" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y96" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z96" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA96" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB96" s="2" t="inlineStr"/>
+      <c r="AC96" s="2" t="inlineStr">
+        <is>
+          <t>—/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr"/>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>沪A52272D</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr"/>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr"/>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q97" s="2" t="inlineStr"/>
+      <c r="R97" s="2" t="inlineStr"/>
+      <c r="S97" s="2" t="inlineStr"/>
+      <c r="T97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="V97" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W97" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y97" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z97" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA97" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB97" s="2" t="inlineStr">
+        <is>
+          <t>145.0</t>
+        </is>
+      </c>
+      <c r="AC97" s="2" t="inlineStr">
+        <is>
+          <t>16/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr"/>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>沪A68895D</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr"/>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr"/>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q98" s="2" t="inlineStr"/>
+      <c r="R98" s="2" t="inlineStr"/>
+      <c r="S98" s="2" t="inlineStr"/>
+      <c r="T98" s="2" t="inlineStr"/>
+      <c r="U98" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="V98" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W98" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y98" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z98" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA98" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB98" s="2" t="inlineStr">
+        <is>
+          <t>153.0</t>
+        </is>
+      </c>
+      <c r="AC98" s="2" t="inlineStr">
+        <is>
+          <t>22/30</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-21-浦东35路.xlsx
+++ b/data/export/2026-10-21-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC98"/>
+  <dimension ref="A1:AC105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,7 +832,7 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -947,17 +947,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>132.5</t>
+          <t>137.3</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1542,17 +1542,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -1667,7 +1667,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1890,22 +1890,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>155.0</t>
+          <t>150.5</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2255,7 +2255,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2382,22 +2382,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -2577,7 +2577,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -2696,7 +2696,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2750,7 +2750,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -2815,7 +2815,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2854,7 +2854,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>170.0</t>
+          <t>164.5</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -3049,7 +3049,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3088,14 +3088,14 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
           <t>148.3</t>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -3168,7 +3168,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3222,7 +3222,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -3283,7 +3283,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3437,22 +3437,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>146.5</t>
+          <t>149.3</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3561,17 +3561,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>146.7</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -3632,7 +3632,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3676,13 +3676,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB27" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>151.0</t>
+        </is>
+      </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -3801,7 +3805,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -3973,7 +3977,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4017,7 +4021,7 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
@@ -4027,7 +4031,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -4092,7 +4096,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4146,7 +4150,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -4211,7 +4215,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4255,17 +4259,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>132.5</t>
+          <t>137.3</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -4511,7 +4515,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -4576,7 +4580,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4615,7 +4619,7 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
@@ -4630,7 +4634,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -4691,7 +4695,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4735,17 +4739,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4864,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4929,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5040,7 +5044,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5079,22 +5083,22 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>155.0</t>
+          <t>150.5</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -5159,7 +5163,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5278,7 +5282,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5332,7 +5336,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -5393,7 +5397,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5432,7 +5436,7 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
@@ -5447,7 +5451,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -5512,7 +5516,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5566,7 +5570,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -5631,7 +5635,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5685,7 +5689,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -5750,7 +5754,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5804,7 +5808,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -5869,7 +5873,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5923,7 +5927,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -5984,7 +5988,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6023,7 +6027,7 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
@@ -6033,12 +6037,12 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>170.0</t>
+          <t>164.5</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -6103,7 +6107,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6157,7 +6161,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -6222,7 +6226,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6261,14 +6265,14 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA49" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
           <t>148.3</t>
@@ -6276,7 +6280,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -6395,7 +6399,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -6460,7 +6464,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6499,22 +6503,22 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA51" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>146.5</t>
+          <t>149.3</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -6633,7 +6637,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -6698,7 +6702,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6742,17 +6746,17 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>132.5</t>
+          <t>137.3</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -6871,7 +6875,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -6936,7 +6940,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6980,17 +6984,17 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -7182,7 +7186,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7236,7 +7240,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -7301,7 +7305,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7420,7 +7424,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7459,22 +7463,22 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -7539,7 +7543,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7593,7 +7597,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -7658,7 +7662,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7712,7 +7716,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -7777,7 +7781,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7831,7 +7835,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -7896,7 +7900,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7935,14 +7939,14 @@
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA63" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
           <t>148.3</t>
@@ -7950,7 +7954,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -8069,7 +8073,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -8134,7 +8138,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8178,17 +8182,17 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>146.7</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -8307,7 +8311,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -8372,7 +8376,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8426,7 +8430,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -8545,7 +8549,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -8610,7 +8614,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8725,7 +8729,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8779,7 +8783,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -8844,7 +8848,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8898,7 +8902,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -9197,7 +9201,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9275,32 +9279,36 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>151分钟</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M75" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9308,7 +9316,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9332,17 +9340,17 @@
       </c>
       <c r="W75" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y75" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z75" s="2" t="inlineStr">
@@ -9352,13 +9360,17 @@
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB75" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>151.0</t>
+        </is>
+      </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -9423,7 +9435,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9462,7 +9474,7 @@
       </c>
       <c r="Z76" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA76" s="2" t="inlineStr">
@@ -9477,7 +9489,7 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -9505,32 +9517,36 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>148分钟</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M77" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -9538,7 +9554,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9562,37 +9578,37 @@
       </c>
       <c r="W77" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z77" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -9630,24 +9646,24 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>18:54</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>170分钟</t>
+          <t>159分钟</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -9657,7 +9673,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9696,7 +9712,7 @@
       </c>
       <c r="Z78" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA78" s="2" t="inlineStr">
@@ -9706,12 +9722,12 @@
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>170.0</t>
+          <t>164.5</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -9739,32 +9755,36 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>155分钟</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M79" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -9772,7 +9792,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9796,37 +9816,37 @@
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y79" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z79" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA79" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>146.5</t>
+          <t>149.3</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -9854,32 +9874,36 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>153分钟</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M80" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9887,7 +9911,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9911,17 +9935,17 @@
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y80" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z80" s="2" t="inlineStr">
@@ -9931,7 +9955,7 @@
       </c>
       <c r="AA80" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB80" s="2" t="inlineStr">
@@ -9941,7 +9965,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -9969,32 +9993,36 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M81" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10002,7 +10030,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10026,17 +10054,17 @@
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y81" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z81" s="2" t="inlineStr">
@@ -10046,17 +10074,17 @@
       </c>
       <c r="AA81" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>132.5</t>
+          <t>137.3</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -10117,7 +10145,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10156,7 +10184,7 @@
       </c>
       <c r="Z82" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA82" s="2" t="inlineStr">
@@ -10171,7 +10199,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -10199,32 +10227,36 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:28</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>148分钟</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr"/>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M83" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -10232,7 +10264,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10256,17 +10288,17 @@
       </c>
       <c r="W83" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y83" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z83" s="2" t="inlineStr">
@@ -10276,17 +10308,17 @@
       </c>
       <c r="AA83" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -10314,32 +10346,36 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:26</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M84" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -10347,7 +10383,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10371,37 +10407,37 @@
       </c>
       <c r="W84" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y84" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z84" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA84" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>155.0</t>
+          <t>150.5</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -10429,32 +10465,36 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:52</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>157分钟</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M85" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10462,7 +10502,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10486,17 +10526,17 @@
       </c>
       <c r="W85" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y85" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z85" s="2" t="inlineStr">
@@ -10506,17 +10546,17 @@
       </c>
       <c r="AA85" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>146.7</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -10577,7 +10617,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10692,7 +10732,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10746,7 +10786,7 @@
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -10807,7 +10847,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10861,7 +10901,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -10922,7 +10962,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -10976,7 +11016,7 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -11037,7 +11077,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11091,7 +11131,7 @@
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -11152,7 +11192,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11267,7 +11307,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11321,7 +11361,7 @@
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -11382,7 +11422,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11436,7 +11476,7 @@
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -11497,7 +11537,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11608,7 +11648,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11662,7 +11702,7 @@
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -11723,7 +11763,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11767,13 +11807,17 @@
       </c>
       <c r="AA96" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB96" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB96" s="2" t="inlineStr">
+        <is>
+          <t>151.0</t>
+        </is>
+      </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -11834,7 +11878,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11888,7 +11932,7 @@
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -11896,22 +11940,22 @@
       <c r="A98" s="2" t="inlineStr"/>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>沪A68895D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
-        <is>
-          <t>19:15</t>
-        </is>
-      </c>
-      <c r="E98" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
@@ -11944,12 +11988,12 @@
       <c r="M98" s="2" t="inlineStr"/>
       <c r="N98" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -11963,45 +12007,850 @@
       <c r="T98" s="2" t="inlineStr"/>
       <c r="U98" s="2" t="inlineStr">
         <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="V98" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W98" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y98" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z98" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA98" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB98" s="2" t="inlineStr">
+        <is>
+          <t>149.3</t>
+        </is>
+      </c>
+      <c r="AC98" s="2" t="inlineStr">
+        <is>
+          <t>21/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr"/>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>沪A68895D</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
           <t>19:15</t>
         </is>
       </c>
-      <c r="V98" s="2" t="inlineStr">
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr"/>
+      <c r="K99" s="2" t="inlineStr"/>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr"/>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P99" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q99" s="2" t="inlineStr"/>
+      <c r="R99" s="2" t="inlineStr"/>
+      <c r="S99" s="2" t="inlineStr"/>
+      <c r="T99" s="2" t="inlineStr"/>
+      <c r="U99" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="V99" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W98" s="2" t="inlineStr">
+      <c r="W99" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X98" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y98" s="2" t="inlineStr">
+      <c r="X99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y99" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z98" s="2" t="inlineStr">
+      <c r="Z99" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA98" s="2" t="inlineStr">
+      <c r="AA99" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB99" s="2" t="inlineStr">
+        <is>
+          <t>153.0</t>
+        </is>
+      </c>
+      <c r="AC99" s="2" t="inlineStr">
+        <is>
+          <t>24/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr"/>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr"/>
+      <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr"/>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P100" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q100" s="2" t="inlineStr"/>
+      <c r="R100" s="2" t="inlineStr"/>
+      <c r="S100" s="2" t="inlineStr"/>
+      <c r="T100" s="2" t="inlineStr"/>
+      <c r="U100" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="V100" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W100" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y100" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z100" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA100" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB98" s="2" t="inlineStr">
-        <is>
-          <t>153.0</t>
-        </is>
-      </c>
-      <c r="AC98" s="2" t="inlineStr">
+      <c r="AB100" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
+      <c r="AC100" s="2" t="inlineStr">
+        <is>
+          <t>2/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr"/>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr"/>
+      <c r="K101" s="2" t="inlineStr"/>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr"/>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P101" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q101" s="2" t="inlineStr"/>
+      <c r="R101" s="2" t="inlineStr"/>
+      <c r="S101" s="2" t="inlineStr"/>
+      <c r="T101" s="2" t="inlineStr"/>
+      <c r="U101" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V101" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W101" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y101" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z101" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA101" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB101" s="2" t="inlineStr">
+        <is>
+          <t>137.5</t>
+        </is>
+      </c>
+      <c r="AC101" s="2" t="inlineStr">
+        <is>
+          <t>11/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr"/>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr"/>
+      <c r="K102" s="2" t="inlineStr"/>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr"/>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P102" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q102" s="2" t="inlineStr"/>
+      <c r="R102" s="2" t="inlineStr"/>
+      <c r="S102" s="2" t="inlineStr"/>
+      <c r="T102" s="2" t="inlineStr"/>
+      <c r="U102" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="V102" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W102" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y102" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z102" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA102" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB102" s="2" t="inlineStr">
+        <is>
+          <t>147.5</t>
+        </is>
+      </c>
+      <c r="AC102" s="2" t="inlineStr">
+        <is>
+          <t>19/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr"/>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr"/>
+      <c r="K103" s="2" t="inlineStr"/>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr"/>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P103" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q103" s="2" t="inlineStr"/>
+      <c r="R103" s="2" t="inlineStr"/>
+      <c r="S103" s="2" t="inlineStr"/>
+      <c r="T103" s="2" t="inlineStr"/>
+      <c r="U103" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="V103" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W103" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y103" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z103" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA103" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB103" s="2" t="inlineStr">
+        <is>
+          <t>164.5</t>
+        </is>
+      </c>
+      <c r="AC103" s="2" t="inlineStr">
+        <is>
+          <t>25/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr"/>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr"/>
+      <c r="K104" s="2" t="inlineStr"/>
+      <c r="L104" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="inlineStr"/>
+      <c r="N104" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P104" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q104" s="2" t="inlineStr"/>
+      <c r="R104" s="2" t="inlineStr"/>
+      <c r="S104" s="2" t="inlineStr"/>
+      <c r="T104" s="2" t="inlineStr"/>
+      <c r="U104" s="2" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="V104" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W104" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y104" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z104" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA104" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB104" s="2" t="inlineStr">
+        <is>
+          <t>148.3</t>
+        </is>
+      </c>
+      <c r="AC104" s="2" t="inlineStr">
+        <is>
+          <t>20/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr"/>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr"/>
+      <c r="K105" s="2" t="inlineStr"/>
+      <c r="L105" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="inlineStr"/>
+      <c r="N105" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O105" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P105" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q105" s="2" t="inlineStr"/>
+      <c r="R105" s="2" t="inlineStr"/>
+      <c r="S105" s="2" t="inlineStr"/>
+      <c r="T105" s="2" t="inlineStr"/>
+      <c r="U105" s="2" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="V105" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W105" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y105" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z105" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA105" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB105" s="2" t="inlineStr">
+        <is>
+          <t>150.5</t>
+        </is>
+      </c>
+      <c r="AC105" s="2" t="inlineStr">
         <is>
           <t>22/30</t>
         </is>

--- a/data/export/2026-10-21-浦东35路.xlsx
+++ b/data/export/2026-10-21-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC105"/>
+  <dimension ref="A1:AC106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2101,7 +2101,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2145,12 +2145,12 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>140.3</t>
+          <t>143.2</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2462,7 +2462,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -2577,7 +2577,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2696,7 +2696,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2815,7 +2815,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3049,7 +3049,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3168,7 +3168,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3517,7 +3517,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>146.7</t>
+          <t>147.7</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -3632,7 +3632,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3977,7 +3977,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4096,7 +4096,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4580,7 +4580,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -4929,7 +4929,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5044,7 +5044,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5163,7 +5163,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5207,12 +5207,12 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>140.3</t>
+          <t>143.2</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
@@ -5282,7 +5282,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5397,7 +5397,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5555,7 +5555,7 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
@@ -5570,7 +5570,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -5635,7 +5635,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5754,7 +5754,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5873,7 +5873,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5988,7 +5988,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6107,7 +6107,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6226,7 +6226,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6464,7 +6464,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -7186,7 +7186,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7305,7 +7305,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7349,12 +7349,12 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>140.3</t>
+          <t>143.2</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
@@ -7424,7 +7424,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7543,7 +7543,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7662,7 +7662,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7781,7 +7781,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7900,7 +7900,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -8138,7 +8138,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8187,12 +8187,12 @@
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>146.7</t>
+          <t>147.7</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -8376,7 +8376,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8614,7 +8614,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8729,7 +8729,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8848,7 +8848,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -9201,7 +9201,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9316,7 +9316,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9435,7 +9435,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9554,7 +9554,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9673,7 +9673,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9792,7 +9792,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9911,7 +9911,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -10145,7 +10145,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10199,7 +10199,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -10383,7 +10383,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10475,12 +10475,12 @@
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>19:52</t>
+          <t>19:55</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>157分钟</t>
+          <t>160分钟</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr"/>
@@ -10502,7 +10502,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>146.7</t>
+          <t>147.7</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -10584,32 +10584,36 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:52</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>152分钟</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M86" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -10617,7 +10621,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10641,17 +10645,17 @@
       </c>
       <c r="W86" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y86" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z86" s="2" t="inlineStr">
@@ -10661,12 +10665,12 @@
       </c>
       <c r="AA86" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>140.3</t>
+          <t>143.2</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
@@ -10732,7 +10736,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10771,7 +10775,7 @@
       </c>
       <c r="Z87" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA87" s="2" t="inlineStr">
@@ -10786,7 +10790,7 @@
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -10847,7 +10851,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10962,7 +10966,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11077,7 +11081,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11192,7 +11196,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11307,7 +11311,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11422,7 +11426,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11537,7 +11541,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11648,7 +11652,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11763,7 +11767,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11878,7 +11882,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11993,7 +11997,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12108,7 +12112,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12223,7 +12227,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12338,7 +12342,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12453,7 +12457,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12507,7 +12511,7 @@
       </c>
       <c r="AC102" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -12568,7 +12572,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12683,7 +12687,7 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
@@ -12798,7 +12802,7 @@
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
@@ -12856,6 +12860,121 @@
         </is>
       </c>
     </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr"/>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="inlineStr"/>
+      <c r="K106" s="2" t="inlineStr"/>
+      <c r="L106" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M106" s="2" t="inlineStr"/>
+      <c r="N106" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O106" s="2" t="inlineStr">
+        <is>
+          <t>19:31</t>
+        </is>
+      </c>
+      <c r="P106" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q106" s="2" t="inlineStr"/>
+      <c r="R106" s="2" t="inlineStr"/>
+      <c r="S106" s="2" t="inlineStr"/>
+      <c r="T106" s="2" t="inlineStr"/>
+      <c r="U106" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="V106" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W106" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y106" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z106" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA106" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB106" s="2" t="inlineStr">
+        <is>
+          <t>147.0</t>
+        </is>
+      </c>
+      <c r="AC106" s="2" t="inlineStr">
+        <is>
+          <t>17/30</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-21-浦东35路.xlsx
+++ b/data/export/2026-10-21-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC106"/>
+  <dimension ref="A1:AC107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -957,7 +957,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1427,17 +1427,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>139.7</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -1552,7 +1552,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -1667,7 +1667,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2397,7 +2397,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2506,17 +2506,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>148.7</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -2577,7 +2577,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -2696,7 +2696,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2740,17 +2740,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>140.2</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -2815,7 +2815,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2969,7 +2969,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -3049,7 +3049,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -3168,7 +3168,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3212,17 +3212,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -3283,7 +3283,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3517,7 +3517,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>147.7</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -3632,7 +3632,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3977,7 +3977,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4096,7 +4096,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4269,7 +4269,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -4515,7 +4515,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -4580,7 +4580,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4749,7 +4749,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -4929,7 +4929,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4973,17 +4973,17 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>139.7</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -5044,7 +5044,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5163,7 +5163,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5282,7 +5282,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5397,7 +5397,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5451,7 +5451,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5560,17 +5560,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>148.7</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -5635,7 +5635,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5689,7 +5689,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -5754,7 +5754,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5798,17 +5798,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>140.2</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -5873,7 +5873,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5912,7 +5912,7 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
@@ -5927,7 +5927,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -5988,7 +5988,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6107,7 +6107,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6151,17 +6151,17 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -6226,7 +6226,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6280,7 +6280,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -6464,7 +6464,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6637,7 +6637,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -6756,7 +6756,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -6875,7 +6875,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -6994,7 +6994,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -7055,7 +7055,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7186,7 +7186,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7240,7 +7240,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -7305,7 +7305,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7424,7 +7424,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7478,7 +7478,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -7543,7 +7543,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7587,17 +7587,17 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>140.2</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -7662,7 +7662,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7716,7 +7716,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -7781,7 +7781,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7825,17 +7825,17 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -7900,7 +7900,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7954,7 +7954,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -8138,7 +8138,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8187,12 +8187,12 @@
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>147.7</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -8311,7 +8311,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -8376,7 +8376,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8549,7 +8549,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -8614,7 +8614,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8658,17 +8658,17 @@
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>139.7</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -8729,7 +8729,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8783,7 +8783,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -8848,7 +8848,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -9090,7 +9090,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9201,7 +9201,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9316,7 +9316,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9435,7 +9435,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9489,7 +9489,7 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9608,7 +9608,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -9673,7 +9673,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9792,7 +9792,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9911,7 +9911,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -10084,7 +10084,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -10145,7 +10145,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10318,7 +10318,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -10383,7 +10383,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10475,19 +10475,19 @@
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>19:55</t>
+          <t>19:53</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>160分钟</t>
+          <t>158分钟</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
@@ -10502,7 +10502,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>147.7</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -10606,12 +10606,12 @@
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -10621,7 +10621,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10703,32 +10703,36 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>152分钟</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M87" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -10736,7 +10740,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10760,17 +10764,17 @@
       </c>
       <c r="W87" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y87" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z87" s="2" t="inlineStr">
@@ -10780,17 +10784,17 @@
       </c>
       <c r="AA87" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>148.7</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -10818,32 +10822,36 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:19</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>159分钟</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M88" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -10851,7 +10859,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10875,17 +10883,17 @@
       </c>
       <c r="W88" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y88" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z88" s="2" t="inlineStr">
@@ -10895,17 +10903,17 @@
       </c>
       <c r="AA88" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>140.2</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -10966,7 +10974,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11048,32 +11056,36 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>141分钟</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M90" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -11081,7 +11093,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11105,17 +11117,17 @@
       </c>
       <c r="W90" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y90" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z90" s="2" t="inlineStr">
@@ -11125,17 +11137,17 @@
       </c>
       <c r="AA90" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -11163,32 +11175,36 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>141分钟</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr"/>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M91" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11196,7 +11212,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11220,17 +11236,17 @@
       </c>
       <c r="W91" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y91" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z91" s="2" t="inlineStr">
@@ -11240,17 +11256,17 @@
       </c>
       <c r="AA91" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>139.7</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -11311,7 +11327,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11365,7 +11381,7 @@
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -11426,7 +11442,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11465,7 +11481,7 @@
       </c>
       <c r="Z93" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA93" s="2" t="inlineStr">
@@ -11480,7 +11496,7 @@
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -11541,7 +11557,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11652,7 +11668,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11706,7 +11722,7 @@
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -11767,7 +11783,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11882,7 +11898,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11997,7 +12013,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12112,7 +12128,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12227,7 +12243,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12281,7 +12297,7 @@
       </c>
       <c r="AC100" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -12342,7 +12358,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12396,7 +12412,7 @@
       </c>
       <c r="AC101" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -12457,7 +12473,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12572,7 +12588,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12687,7 +12703,7 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
@@ -12741,7 +12757,7 @@
       </c>
       <c r="AC104" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -12802,7 +12818,7 @@
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
@@ -12917,7 +12933,7 @@
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P106" s="2" t="inlineStr">
@@ -12961,17 +12977,132 @@
       </c>
       <c r="AA106" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB106" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>148.7</t>
         </is>
       </c>
       <c r="AC106" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>20/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr"/>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>20:55</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="inlineStr"/>
+      <c r="K107" s="2" t="inlineStr"/>
+      <c r="L107" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M107" s="2" t="inlineStr"/>
+      <c r="N107" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O107" s="2" t="inlineStr">
+        <is>
+          <t>20:20</t>
+        </is>
+      </c>
+      <c r="P107" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q107" s="2" t="inlineStr"/>
+      <c r="R107" s="2" t="inlineStr"/>
+      <c r="S107" s="2" t="inlineStr"/>
+      <c r="T107" s="2" t="inlineStr"/>
+      <c r="U107" s="2" t="inlineStr">
+        <is>
+          <t>20:55</t>
+        </is>
+      </c>
+      <c r="V107" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W107" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X107" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y107" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z107" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA107" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB107" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
+      <c r="AC107" s="2" t="inlineStr">
+        <is>
+          <t>1/30</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-21-浦东35路.xlsx
+++ b/data/export/2026-10-21-浦东35路.xlsx
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,17 +832,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>144.3</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -1667,7 +1667,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>141.2</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1905,7 +1905,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -2155,7 +2155,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2462,7 +2462,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -2577,7 +2577,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2621,17 +2621,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -2815,7 +2815,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2859,17 +2859,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>164.5</t>
+          <t>152.3</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2974,17 +2974,17 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -3049,7 +3049,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -3168,7 +3168,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:23</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3222,7 +3222,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -3283,7 +3283,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3327,13 +3327,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB24" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>151.0</t>
+        </is>
+      </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -3398,7 +3402,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3452,7 +3456,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -3571,7 +3575,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -3632,7 +3636,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3676,17 +3680,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>151.0</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -3977,7 +3981,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4021,17 +4025,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>144.3</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -4150,7 +4154,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -4580,7 +4584,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4634,7 +4638,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4868,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -5044,7 +5048,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5098,7 +5102,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -5217,7 +5221,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -5282,7 +5286,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5326,12 +5330,12 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>141.2</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -5397,7 +5401,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5441,7 +5445,7 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
@@ -5516,7 +5520,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5570,7 +5574,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -5635,7 +5639,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5679,17 +5683,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -5873,7 +5877,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5917,17 +5921,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -5988,7 +5992,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6032,17 +6036,17 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>164.5</t>
+          <t>152.3</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -6107,7 +6111,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:23</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6161,7 +6165,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -6226,7 +6230,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6280,7 +6284,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -6464,7 +6468,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6518,7 +6522,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -6875,7 +6879,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -7055,7 +7059,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7359,7 +7363,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -7424,7 +7428,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7662,7 +7666,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7706,17 +7710,17 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -7781,7 +7785,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:23</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7835,7 +7839,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -7900,7 +7904,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7954,7 +7958,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -8192,7 +8196,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -8430,7 +8434,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -8549,7 +8553,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -8848,7 +8852,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8892,12 +8896,12 @@
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>141.2</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
@@ -9090,7 +9094,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9201,7 +9205,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9245,13 +9249,17 @@
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB74" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>151.0</t>
+        </is>
+      </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -9316,7 +9324,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9360,17 +9368,17 @@
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>151.0</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -9435,7 +9443,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9479,7 +9487,7 @@
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB76" s="2" t="inlineStr">
@@ -9554,7 +9562,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9673,7 +9681,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9717,17 +9725,17 @@
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>164.5</t>
+          <t>152.3</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -9792,7 +9800,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9846,7 +9854,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -9911,7 +9919,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9955,17 +9963,17 @@
       </c>
       <c r="AA80" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>144.3</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -10145,7 +10153,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10199,7 +10207,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -10383,7 +10391,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10437,7 +10445,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -10556,7 +10564,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -10675,7 +10683,7 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -10740,7 +10748,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10794,7 +10802,7 @@
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -11028,7 +11036,7 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -11093,7 +11101,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:23</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11147,7 +11155,7 @@
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -11409,32 +11417,36 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:33</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr"/>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M93" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -11442,7 +11454,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11466,17 +11478,17 @@
       </c>
       <c r="W93" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y93" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z93" s="2" t="inlineStr">
@@ -11486,17 +11498,17 @@
       </c>
       <c r="AA93" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -11524,32 +11536,36 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:56</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>151分钟</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr"/>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M94" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11557,7 +11573,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11581,17 +11597,17 @@
       </c>
       <c r="W94" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y94" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z94" s="2" t="inlineStr">
@@ -11601,13 +11617,17 @@
       </c>
       <c r="AA94" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB94" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>151.0</t>
+        </is>
+      </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -11635,32 +11655,36 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:53</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr"/>
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M95" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -11668,7 +11692,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11692,17 +11716,17 @@
       </c>
       <c r="W95" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y95" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z95" s="2" t="inlineStr">
@@ -11712,17 +11736,17 @@
       </c>
       <c r="AA95" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB95" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -11750,32 +11774,36 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr"/>
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M96" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11783,7 +11811,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11807,17 +11835,17 @@
       </c>
       <c r="W96" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y96" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z96" s="2" t="inlineStr">
@@ -11827,17 +11855,17 @@
       </c>
       <c r="AA96" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB96" s="2" t="inlineStr">
         <is>
-          <t>151.0</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -11865,32 +11893,36 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr"/>
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M97" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -11898,7 +11930,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11922,17 +11954,17 @@
       </c>
       <c r="W97" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y97" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z97" s="2" t="inlineStr">
@@ -11942,12 +11974,12 @@
       </c>
       <c r="AA97" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>141.2</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
@@ -11980,12 +12012,12 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程48%处后消失；随后反向物理轨迹由seq28推进至seq50，推进22站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
@@ -12013,7 +12045,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12021,10 +12053,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q98" s="2" t="inlineStr"/>
-      <c r="R98" s="2" t="inlineStr"/>
-      <c r="S98" s="2" t="inlineStr"/>
-      <c r="T98" s="2" t="inlineStr"/>
+      <c r="Q98" s="2" t="inlineStr">
+        <is>
+          <t>物理seq31（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R98" s="2" t="inlineStr">
+        <is>
+          <t>20:13</t>
+        </is>
+      </c>
+      <c r="S98" s="2" t="inlineStr">
+        <is>
+          <t>20:22</t>
+        </is>
+      </c>
+      <c r="T98" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq31映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±9分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="U98" s="2" t="inlineStr">
         <is>
           <t>19:10</t>
@@ -12067,7 +12115,7 @@
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -12095,32 +12143,36 @@
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr"/>
       <c r="K99" s="2" t="inlineStr"/>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M99" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N99" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -12128,7 +12180,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12152,17 +12204,17 @@
       </c>
       <c r="W99" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y99" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z99" s="2" t="inlineStr">
@@ -12172,17 +12224,17 @@
       </c>
       <c r="AA99" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB99" s="2" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>144.3</t>
         </is>
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -12210,32 +12262,36 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr"/>
       <c r="K100" s="2" t="inlineStr"/>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M100" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N100" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -12243,7 +12299,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12267,17 +12323,17 @@
       </c>
       <c r="W100" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y100" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z100" s="2" t="inlineStr">
@@ -12287,7 +12343,7 @@
       </c>
       <c r="AA100" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB100" s="2" t="inlineStr">
@@ -12358,7 +12414,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12473,7 +12529,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12527,7 +12583,7 @@
       </c>
       <c r="AC102" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -12555,32 +12611,36 @@
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:48</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr"/>
       <c r="K103" s="2" t="inlineStr"/>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M103" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N103" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -12588,7 +12648,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12612,17 +12672,17 @@
       </c>
       <c r="W103" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X103" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y103" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z103" s="2" t="inlineStr">
@@ -12632,17 +12692,17 @@
       </c>
       <c r="AA103" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB103" s="2" t="inlineStr">
         <is>
-          <t>164.5</t>
+          <t>152.3</t>
         </is>
       </c>
       <c r="AC103" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -12703,7 +12763,7 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
@@ -12757,7 +12817,7 @@
       </c>
       <c r="AC104" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -12818,7 +12878,7 @@
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
@@ -12872,7 +12932,7 @@
       </c>
       <c r="AC105" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -12933,7 +12993,7 @@
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P106" s="2" t="inlineStr">
@@ -12987,7 +13047,7 @@
       </c>
       <c r="AC106" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -13048,7 +13108,7 @@
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P107" s="2" t="inlineStr">
@@ -13092,17 +13152,17 @@
       </c>
       <c r="AA107" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB107" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC107" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
